--- a/data/jobs_master.xlsx
+++ b/data/jobs_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W42"/>
+  <dimension ref="A1:W50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5618,6 +5618,1010 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>alio-304901</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>국립중앙의료원</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>계약직 연구원/행정(응급취약지·지역협력팀, 강원응급의료지원센터, 전북응급의료지원센터, 충북응급의료지원센터) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>서울,강원,충북,전북</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>비정규직</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>보건.의료</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>신입+경력</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>대졸(4년)</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>장애인, 보훈대상자는 관계 법령에 따라 우대합니다.</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>https://nmc.recruiter.co.kr/app/jobnotice/view?systemKindCode=MRS2&amp;jobnoticeSn=266365</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 계약직 연구원(응급취약지·지역협력팀)
+[필수]
+간호학, 의(료)공학, 보건학, 통계학, 행정학 학사학위 취득자(졸업예정자 미포함)
+[학위 인정 범위]
+- 졸업증명서 또는 학위수여증명서 상에 해당 학위가 ‘간호학’ 또는 ‘의(료)공학’ 또는 ‘보건학’또는 ‘통계학’ 또는 ‘행정학’인 경우
+- 졸업증명서 또는 학위수여증명서 상 전공(학과)명에 ‘간호’ 또는 ‘의(료)공’ 또는 ‘보건’ 또는 ‘통계’ 또는 ‘행정’이 포함된 경우
+2. 계약직 연구원(강원응급의료지원센터)
+[필수]
+· 보건학, 행정학, 통계학, 사회(복지)학 학사 학위 이상 소지자(졸업예정자 미포함)
+· 강원특별자치도 원주시 근무가능자
+[학위 인정 범위]
+- 졸업증명서 또는 학위수여증명서 상에 해당 학위가 ‘보건학’ 또는 ‘행정학’ 또는 ‘통계학’또는 ‘사회(복지)학’인 경우
+- 졸업증명서 또는 학위수여증명서 상 전공(학과)명에 ‘보건’ 또는 ‘행정’ 또는 ‘통계’ 또는 ‘사회(복지)’가 포함된 경우
+3. 계약직 연구원(전북응급의료지원센터)
+[필수]
+· 보건학, 의료정보학, 통계학, 경영학 학사 학위 이상 소지자(졸업예정자 미포함)
+· 전북특별자치도 근무 가능자
+[학위 인정 범위]
+- 졸업증명서 또는 학위수여증명서 상에 해당 학위가 ‘보건학’ 또는 ‘의료정보학’ 또는 ‘통계학’또는 ‘경영학’ 인 경우
+- 졸업증명서 또는 학위수여증명서 상 전공(학과)명에 ‘보건’ 또는 ‘의료정보’ 또는 ‘통계’ 또는 ‘경영’이 포함된 경우
+4. 계약직 연구원(충북응급의료지원센터)
+[필수] 
+아래의 두 조건 중 한 가지 이상을 충족하는 자이면서 충북 청주시 근무 가능자
+· 간호사, 1급 응급구조사, 보건의료정보관리사, 임상병리사, 방사선사 면허·자격 중 1개 이상 소지자
+· 의(료)공학, 통계학 전문학사 학위 이상 소지자
+[학위 인정 범위]
+- 졸업증명서 또는 학위수여증명서 상에 해당 학위가 ‘의(료)공학’ 또는 ‘통계학’인 경우
+- 졸업증명서 또는 학위수여증명서 상 전공(학과) 명에 ‘의(료)공’ 또는 ‘통계’ 가 포함된 경우
+5. 계약직 행정(전북응급의료지원센터)
+[필수]
+· 보건학, 행정학, 법학, 회계학 학사 학위 이상 소지자(졸업예정자 미포함)
+· 전북특별자치도 근무 가능자
+[학위 인정 범위]
+- 졸업증명서 또는 학위수여증명서 상에 해당 학위가 ‘보건학’ 또는 ‘행정학’ 또는 ‘법학’또는 ‘회계학’ 인 경우
+- 졸업증명서 또는 학위수여증명서 상 전공(학과)명에 ‘보건’ 또는 ‘행정’ 또는 ‘법’ 또는 ‘회계’가 포함된 경우
+</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>우대조건은 공고문을 확인하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>대졸(4년)</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>통계</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>비정규직</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>alio-304900</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>국립중앙의료원</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>계약직 간호사/응급구조사(경기응급의료지원센터-휴직대체, 세종응급의료지원센터, 부울경남광역응급의료상황팀, 서울인천광역응급의료상황팀) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>서울,부산,세종,경기</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>비정규직</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>보건.의료</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>신입+경력</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>장애인, 보훈대상자는 관계 법령에 따라 우대합니다.</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>https://nmc.recruiter.co.kr/app/jobnotice/view?systemKindCode=MRS2&amp;jobnoticeSn=266364</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. 계약직(휴직대체) 간호사/응급구조사(경기응급의료지원센터)
+[필수]
+· 간호사 면허 또는 1급 응급구조사 자격 소지자
+· 경기지역 근무 가능자(최초 근무지: 국민건강보험공단일산병원)
+2. 계약직 간호사/응급구조사(세종응급의료지원센터)
+[필수]
+· 간호사 또는 1급 응급구조사 자격(면허) 소지자
+· 세종지역 근무 가능 자 
+3. 계약직 간호사/응급구조사(부울경남광역응급의료상황팀)
+[필수] 아래의 필수 응시자격을 모두 충족하는 자
+· 간호사 면허 또는 1급 응급구조사 자격 소지자
+· 3교대 근무 가능자
+· 부산지역 근무가능자
+4. 계약직 간호사/응급구조사(서울인천광역응급의료상황팀)
+[필수] 아래의 필수 응시자격을 모두 충족하는 자
+· 간호사 면허 또는 1급 응급구조사 자격 소지자
+· 3교대 근무 가능자
+· 서울지역 근무가능자
+</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>우대조건은 공고문을 확인하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>비정규직</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>alio-304898</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>(재)한국우편사업진흥원</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>한국우편사업진흥원 2026년 기간제계약직(청년인턴, 사회형평(장애, 보훈)) 채용</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>비정규직,청년인턴(체험형)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>사업관리,경영.회계.사무,문화.예술.디자인.방송,영업판매,인쇄.목재.가구.공예</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>신입</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>o 장애인, 국가유공자, 저소득층 등 관련 법률에 따른 대상자 우대
+o 분야별 관련 교육ㆍ경력ㆍ자격사항 우대
+※ 자세한 사항은 공고문, 직무기술서 참고</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>https://posa.incruit.com/</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>[전 채용분야 공통사항]
+o 학력, 전공, 학점, 성별, 어학성적 등 제한 없음
+※ 직무에 따라 별도 자격 요구 가능, 직무별 지원자격 별도 확인 필수
+o 진흥원 인사규정 제15조(결격사유)에 해당하지 않는 자
+※ 붙임. 한국우편사업진흥원 인사규정 제15조(결격사유) 참고
+o 임용일(2026. 11. 30.)부터 근무 가능한 자
+o 임용일(2026. 11. 30.) 기준 「근로기준법」 제64조(최저 연령과 취직인허증)에 해당하지 않는 자
+o 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자
+[체험형 청년인턴 분야]
+o (공통자격) 청년: 임용일 기준 「청년고용촉진 특별법 시행령」에 따른 청년(만 15세 이상 34세 이하)에 해당하는 자
+※ 「제대군인지원에 관한 법률 시행령」 제19조(응시연령 상한 연장)에 따라 제대군인의 경우 복무기간에 따라 응시연령 상한을 연장 적용할 수 있음
+① 2년 이상의 복무기간을 마치고 전역한 제대군인: 3세 
+② 1년 이상 2년 미만의 복무기간을 마치고 전역한 제대군인: 2세 
+③ 1년 미만의 복무기간을 마치고 전역한 제대군인: 1세
+o (별도자격) 일반 행정 지원[사회형평(자립준비청년) 제한경쟁], 문화우편상품 디자인[자격 제한경쟁]
+- 일반 행정 지원(자립준비청년): 「아동복지법」에 따른 자립준비청년에 해당하며, 관련 증빙서류 제출이 가능한 자
+※ 자립수당수급자확인서, 보호종료확인서, 보호시설 퇴소확인서 중 1부
+- 문화우편상품 디자인: Adobe Photoshop, Illustrator 프로그램 활용 가능한 자
+[기간제 계약직(사회형평: 장애, 보훈) 분야]
+o 장애: 「장애인고용촉진 및 직업재활법」 및 「장애인복지법」에 따른 등록장애인 또는 「장애인고용촉진 및 직업재활법 시행령」에 따른 상이등급 기준에 해당하는 자로서 관련 증명서 발급이 가능한 자
+o 보훈: 「국가유공자 등 예우 및 지원에 관한 법률」 등 관련 법령에 따른 취업지원 대상자로서 관련 증명서 발급이 가능한 자</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>장애인, 국가유공자, 저소득층 등 관련 법률에 따른 대상자 우대</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>비정규직,청년인턴(체험형)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>alio-304896</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>(재)한국우편사업진흥원</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>한국우편사업진흥원 2026년 신입직원(일반직, 전문직(사무), 전문직(특수)) 채용</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>서울,대전</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>정규직,무기계약직</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>사업관리,경영.회계.사무,문화.예술.디자인.방송,영업판매,정보통신,인쇄.목재.가구.공예,환경.에너지.안전</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>신입</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>o 장애인, 국가유공자, 저소득층 등 관련 법률에 따른 대상자 우대
+o 한국우편사업진흥원 청년인턴 수료자 우대
+o 분야별 관련 교육ㆍ경력ㆍ자격사항 우대
+※ 자세한 사항은 공고문, 직무기술서 참고</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>https://posa.incruit.com/</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>[전 채용분야 공통사항]
+o 학력, 전공, 학점, 성별, 어학성적 등 제한 없음
+※ 직무에 따라 별도 자격 요구 가능, 직무별 지원자격 별도 확인 필수
+o 진흥원 인사규정 제15조(결격사유)에 해당하지 않는 자
+※ 붙임. 한국우편사업진흥원 인사규정 제15조(결격사유) 참고
+o 임용일(2026. 11. 30.)부터 근무 가능한 자
+o 임용일(2026. 11. 30.) 기준 진흥원 인사규정상 정년에 이르지 않고, 「근로기준법」 제64조(최저 연령과 취직인허증)에 해당하지 않는 자
+o 「병역법」 제76조에서 정한 병역의무 불이행 사실이 없는 자</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>장애인, 국가유공자, 저소득층 등 관련 법률에 따른 대상자, 한국우편사업진흥원 청년인턴 수료자 우대</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>정규직,무기계약직</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>alio-304892</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>국립중앙의료원</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>의사직 및 계약직 전문의 채용 재공고(내분비대사내과, 중환자전담전문의, 소아청소년과(신생아분과))</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>정규직,비정규직</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>보건.의료</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>신입+경력</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>대졸(4년)</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>장애인, 보훈대상자는 관계 법령에 따라 우대합니다.</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>https://nmc.recruiter.co.kr/app/jobnotice/view?systemKindCode=MRS2&amp;jobnoticeSn=266348</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>1. 내분비대사내과 전문의(의사직 1~3급) 1명
+[필수]
+· 의사면허 및 내과 전문의 자격 소지자
+· 내분비대사내과 분과 전문의 자격 소지자
+2. 내과계 중환자실 전담 전문의(의사직 1~3급) 2명
+[필수]
+- 의사 면허 소지자로서 아래 조건 중 하나 이상을 충족하는 자
+- 내과 전문의 자격 소지자
+- 신경과 전문의 자격 소지자
+- 응급의학과 전문의 자격 소지자
+[우대]
+- 중환자의학 세부전문의 자격 소지자
+3. 소아청소년과-신생아분과 계약직 전문의 1명
+채용분야 : 소아청소년과 (신생아실 담당)
+[필수] 
+ · 의사 면허 및 소아청소년과 전문의 자격 소지자
+ · 신생아 분과전문의 자격 소지자 혹은 종합병원 또는 상급종합병원 신생아 집중치료실 1년 이상 근무경력을 보유한 자</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>우대조건은 공고문을 확인하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>대졸(4년)</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>정규직,비정규직</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>alio-304890</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>예술의전당</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026년도 4차 예술의전당 직원 블라인드 채용</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>무기계약직,비정규직</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>문화.예술.디자인.방송,경비.청소,환경.에너지.안전</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>신입+경력</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>□ 보훈대상자 우대
+□ 장애인 우대
+□ 예술의전당 계약직, 용역직 근무경력 1년 이상인 자 우대
+□ 예술의전당 청년인턴, 하우스어텐던트 수료자 우대
+□ 직무관련 전문 자격증 및 어학성적 보유자 우대
+* 세부사항은 채용사이트 및 공고문 참조</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>https://sac.hrdms.kr/#/</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>응시자격(공통)
+□ 학력·성별·지역 제한 없음
+□ 공고일 기준, 만 18세 이상이며 정년에 도달하지 않은 자
+  - 정년기준: 만 60세 (보안경비·환경미화는 만 65세)
+□ 최종합격자 발표 이후 즉시 근무 가능한 자(‘26.11.3. 예정)
+□ 병역의무대상자는 군필 또는 면제자
+□ 당사 인사관리규정의 결격사유에 해당사항이 없는 자</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>보훈대상자, 장애인, 예술의전당 근무경력자, 전문 자격증 및 어학성적 보유자</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>무기계약직,비정규직</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>alio-304888</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>(재)우체국물류지원단</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>우체국물류지원단 서울지사 동서울물류사업소 추석 단기 기간제(일용직) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>비정규직</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>운전.운송</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>신입+경력</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>https://www.pola.or.kr</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">□ 우체국물류지원단 인사규정에 따른 결격사유가 없는 자
+□ 채용 즉시 근무가 가능한 자
+□ 연령제한 없음 </t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>비정규직</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>alio-304886</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>국민연금공단</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026년 하반기 공무직 공개채용 공고</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>서울,부산,인천,대전,세종,경기,강원,충북,전북,전남광주,경남</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>무기계약직</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>경영.회계.사무,보건.의료,정보통신</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>신입</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>○ 「국가유공자 등 예우 및 지원에 관한 법률」 등 관련 법률에 따른 취업지원대상자(전 전형 우대)
+  - 동일분야·지역별 채용인원이 4명 이상인 경우 가점 부여하고, 4명 미만은 동점자 발생 시 우대하되 응시자 수가 채용예정인원과 같거나 그보다 적은 경우 가점 적용
+○ 「장애인고용촉진 및 직업재활법 시행령」 제3조 및 제4조에 따른 장애인(전 전형 우</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>https://nps.saramin.co.kr</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>[공통 자격]
+○ 연령·성별·학력 등 제한 없음
+   * 단, 임용일 기준 공단 정년(60세) 이상자는 제외
+○ 대한민국 국적을 보유한 사람
+○ 공단 「인사규정」 제11조(결격사유)에 해당하지 않는 사람
+○ 임용(예정)일부터 근무가 가능한 사람
+[직렬별 자격]
+○ 사업장상담직 : 공통자격 이외의 별도 요건 없음
+○ 지역상담직 : 공통자격 이외의 별도 요건 없음
+○ 근로능력평가직(활동능력평가) : 공통자격 이외의 별도 요건 없음
+○ 근로능력평가직(의학적평가) : 간호사, 물리치료사, 임상병리사, 작업치료사 중 1개 이상 면허를 소지한 사람
+○ 장애등록상담직 : 공통자격 이외의 별도 요건 없음
+○ 고객센터상담직(가): 한글타자능력 분당 200타 이상, 정확도 90% 이상</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>아래 [우대내용] 참고</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>무기계약직</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/jobs_master.xlsx
+++ b/data/jobs_master.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W50"/>
+  <dimension ref="A1:W63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6622,6 +6622,1620 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>alio-304959</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한국연구재단</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>한국연구재단 2026년도 체험형 청년인턴(장애) 및 제7차 사업위촉직 채용 공고</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>서울,대전</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>비정규직,청년인턴(체험형)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>사업관리,경영.회계.사무</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>신입+경력</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>국가유공자, 장애인, 비수도권 지역인재, 저소득층, 북한이탈주민, 다문화가족, 자립준비청년 우대
+※ 우대사항(가산점) 세부 기준은 공고문 참조 요망</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>https://www.nrf.re.kr/page/54?ac=view&amp;postNo=281963&amp;pageNum=1&amp;searchType=&amp;searchText=&amp;menuNo=54&amp;boardNo=7&amp;menuTypeCd=MENU_TYPE_02&amp;code=</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>1. 공통
+- 한국연구재단 인사규정 제9조(결격사유) 각 호에 해당하지 않는 자로 정년을 고려하여 만61세 미만(접수마감일 기준)인 자
+- 모집분야별 지원자격 및 관련 직무역량을 보유한 사람 중 2026.11.1.(일)자로 임용이 가능하고, 2026.11.2.(월)부터 정산근무가 가능한 자(채용 분야별 중복지원 불가)
+- 업무수행을 위한 오피스 프로그램(한글, 엑셀 등) 활용이 가능한 자
+2. 체험형 청년인턴(장애)
+- 임용일 기준(2026.11.1.) 청년고용촉진특별법 제2조에 근거한 청년(만 15세 이상 만 34세 이하에 해당하는 자
+- 단, 제대군인지원에 관한 법률 제16조 제1항 및 동법 시행령 제19조에 따라 최대 3살 범위에서 응시연령 상한 연장 가능
+ → 2년 이상의 복무기간을 마치고 전역한 제대군인: 3세
+ → 1년 이상 2년 미만의 복무기간을 마치고 전역한 제대군인: 2세
+ → 1년 미만의 복무기간을 마치고 전역한 제대군인: 1세
+- 공고일 이전 한국연구재단 인턴 유경험자 및 현재 인턴근무 중인 자는 지원 불가</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>국가유공자, 장애인, 비수도권지역인재, 저소득층, 북한이탈주민, 다문화가족, 자립준비청년</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>엑셀</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>비정규직,청년인턴(체험형)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>alio-304958</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한국토지주택공사</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026년 하반기 한국토지주택공사 신입사원(5·6급) 공채</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>서울,부산,대구,인천,대전,울산,세종,경기,강원,충북,충남,전북,전남광주,경북,경남,제주</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>청년인턴(채용형)</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>사업관리,경영.회계.사무,법률.경찰.소방.교도.국방,사회복지.종교,문화.예술.디자인.방송,영업판매,건설,기계,화학,전기.전자,정보통신,환경.에너지.안전</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>신입</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>학력무관,고졸</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ㅇ (특별우대) 취업지원대상자(국가유공자법 등), 장애인, 저소득층, 북한이탈주민, 다문화가족, 자립준비청년, 이전지역인재 등 서류전형 등 전형별 만점의 5%~10% 가산점 부여
+ㅇ (일반우대) 고급자격증 소지자, 공사가 주최한 공모전 수상자 등 전형별 만점의 3%~10% 가산점 부여, 해당자 전원 서류전형 면제
+ㅇ (청년인턴) 탁월-서류전형 면제 및 </t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>https://www.lh.or.kr</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>□ 5급 일반·보훈
+ㅇ 자격증
+ - 사무직(일반행정, 전문-법률·회계) : 제한없음
+ - 사무직(전문-전산·국가유산), 기술직(전체) : 해당 모집직무 지원자격 자격증 보유자
+ㅇ (보훈전형) 「국가유공자 등 예우 및 지원에 관한 법률」 등에 따른 취업지원대상자
+□ 5급 장애인
+ㅇ (기본자격) 「장애인고용촉진 및 직업재활법」에 따른 장애인
+ㅇ 자격증
+ - 사무직(일반행정) : 제한없음
+ - 기술직(전체) : 해당 모집직무 지원자격 자격증 보유자
+ ※ 기술직 지원자의 경우 본인이 선택한 모집직무의 지원자격을 보유해야함
+ ※ 장애인 지원자격과 관련하여 허위 사실이 발견된 경우 합격취소 및 직권면직될 수 있음
+□ 5급 공통
+ ㅇ 성별, 신체조건, 학력, 연령 등 제한없음
+ ㅇ 공사 직원채용 결격사유에 해당되지 않는 자
+ ㅇ (병역) 남자의 경우 병역필 또는 면제자
+ ※ 단, ‘26.12.27까지 전역예정자로서 전형절차에 응시 가능한 경우에 지원 가능
+ ㅇ ‘26.12.28부터 전일근무가 가능하고 인턴기간 중 3주 내외 합숙교육이 가능한 자
+ ※ 지원자격 등 입사지원서상 기재사항이 허위로 판명될 경우 불합격 처리 등 불이익을 받을 수 있음
+□ 6급 일반·보훈
+ㅇ (학력) 고교졸업예정자 및 최종학력이 고졸인 자(고교 검정고시 합격자 및 대학 중퇴자, 대학 재학·휴학자 포함)
+ * 공고일 기준 대학(전문대학 포함) 졸업자 및 졸업학년 2학기 재학 이상인 자는 지원할 수 없으며, 별도 수업 없이 대학 졸업이 가능한 경우도 졸업한 것으로 간주하여 고졸자에서 제외
+ㅇ (보훈전형) 「국가유공자 등 예우 및 지원에 관한 법률」등에 따른 취업지원대상자
+□ 6급 장애인
+ㅇ (기본자격) 「장애인고용촉진 및 직업재활법」에 따른 장애인
+ㅇ (학력) 고교졸업예정자 및 최종학력이 고졸인 자(고교 검정고시 합격자 및 대학 중퇴자, 대학 재학·휴학자 포함)
+ * 공고일 기준 대학(전문대학 포함) 졸업자 및 졸업학년 2학기 재학 이상인 자는 지원할 수 없으며, 별도 수업 없이 대학 졸업이 가능한 경우도 졸업한 것으로 간주하여 고졸자에서 제외
+□ 6급 공통
+ ㅇ 성별, 신체조건, 연령 등 제한없음
+ ㅇ 공사 직원채용 결격사유에 해당되지 않는 자
+ ㅇ (병역) 병역을 기피한 사실이 없는 자
+ ※ 병역 미필자도 지원 가능하며, 현재 군 복무중인 자는 ‘26.12.27까지 전역예정자로서 전형절차에 응시 가능한 경우에 지원 가능
+ ㅇ ‘26.12.28부터 전일근무가 가능하고 인턴기간 중 3주 내외 합숙교육이 가능한 자
+ ※ 6급공채 및 장애인 자격과 관련하여 허위 사실이 발견된 경우 합격취소 및 직권면직될 수 있으며, 
+ ※ 지원자격 등 입사지원서상 기재사항이 허위로 판명될 경우 불합격 처리 등 불이익을 받을 수 있음
+* 보다 자세한 사항은 공고문 참조</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>ㅇ (특별우대) 취업지원대상자(국가유공자법 등), 장애인, 저소득층, 북한이탈주민, 다문화가족, 자립준비청년, 이전지역인재 등 서류전형 등 전형별 만점의 5%~10% 가산점 부여, ㅇ (일반우대) 고급자격증 소지자, 공사가 주최한 공모전 수상자 등 전형별 만점의 3%~10% 가산점 부여, 해당자 전원 서류전형 면제, ㅇ (청년인턴) 탁월-서류전형 면제 및 필기전형 만점의 3%, 우수-서류전형 면제, 성실-서류전형 만점의 5% 가산점 부여  * 보다 자세한 사항은 공고문 참조</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>학력무관,고졸</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>청년인턴(채용형)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>alio-304956</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>국가아동권리보장원</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>(제2026-2호) 국가아동권리보장원 직원 채용</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>서울,경기</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>정규직,비정규직</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>사업관리,경영.회계.사무,사회복지.종교,문화.예술.디자인.방송,정보통신</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>신입+경력</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>학력무관,대졸(4년)</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>○ 가점 적용
+&lt;공통&gt;
+- 취업지원대상자: 전형별 만점의 5% 또는 10%
+- 장애인
+  1) 심한 장애: 전형별 만점의 10%
+  2) 심하지 않은 장애: 전형별 만점의 5%
+- 자립준비청년: 전형별 만점의 5%
+- 한국사능력검정시험 2급 이상 인증서 소지자: 서류전형 만점의 2%
+&lt;정규직 채용 분야&gt;
+- 비수도권지역인재: 서류전형 만</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>https://www.ncrc.or.kr/ncrc/na/ntt/selectNttInfo.do?mi=1548&amp;bbsId=1012&amp;nttSn=11054&amp;cataGori=&amp;tabName=</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>[공통 응시자격]
+- 성별, 연령 제한 없음(단, 임용예정일(당일 포함) 기준 보장원 정년인 만 60세 이상자는 응시 불가)
+- 국가아동권리보장원 「인사규정」에 따른 채용 결격사유에 해당하지 않는 자
+- 「아동·청소년의 성보호에 관한 법률」 제56조, 「아동복지법」 제29조의3 및 「장애인복지법」 제59조의3의 취업제한 대상에 해당하지 않는 자
+- 「병역법」 제76조의 병역의무 불이행자에 해당하지 않는 자
+[채용분야 응시자격]
+○ 경영전략본부총괄(개방형직위) 1급상당, 아동보호본부총괄(개방형직위) 1급상당, 아동지원본부총괄(개방형직위) 1급상당
+ 다음 각 자격요건 중 하나 이상에 해당하는 자
+  - 국가 또는 지방공무원 4급직 이상에 재직한 자
+  - 국가 또는 지방공무원 5급에 5년 이상 재직한 자
+  - 공공기관 또는 정부투자기관에서 1급 상당직으로 재직한 자
+  - 사회복지 관련 기관 또는 임용예정부서 관련 업무 분야에서 15년 이상 근무한 자로서 부장급 이상의 경력이 있는 자
+○ 사업관리(입양기록물관리) 4급
+ 아래의 자격요건을 모두 충족하는 자(①+②)
+ ① 다음의 어느 하나에 따라 기록물관리 전문요원 자격증을 소지한 자
+  - 기록관리학 전공으로 석사학위 이상을 취득한 자
+  - 기록관리학 학사학위 취득자, 역사학 또는 문헌정보학 학사학위 이상 취득자로서 행정안전부령으로 정하는 기록관리학 교육과정을 이수하고, 행정안전부장관이 시행하는 기록물관리 전문요원 시험에 합격한 자
+ ② 다음 각 자격요건 중 하나 이상에 해당하는 자
+  - 국가 또는 지방공무원 7급직 이상에 재직한 자
+  - 국가 또는 지방공무원 8급에 3년 이상 재직한 자
+  - 공공기관 또는 정부투자기관에서 4급 상당직으로 재직한 자
+  - 기록물관리 관련 업무 분야에서 4년 이상 근무한 자
+○ 기관운영(정보화전략) 4급
+ 아래의 자격요건을 모두 충족하는 자(①+②)
+ ① 컴퓨터·통신 관련학과* 학사 학위 이상 소지자로서, 해당 직무를 수행할 수 있다고 인정되는 자
+    * (관련학과) 정보보호(보안)학, 정보통신공학, 컴퓨터공학, 소프트웨어공학, 전산학 등 전산공학계열 전공
+ ② 다음 각 자격요건 중 하나 이상에 해당하는 자
+  - 국가 또는 지방공무원 7급직 이상에 재직한 자
+  - 국가 또는 지방공무원 8급에 3년 이상 재직한 자
+  - 공공기관 또는 정부투자기관에서 4급 상당직으로 재직한 자
+  - 정보기술(IT) 관련 업무 분야에서 4년 이상 근무한 자
+○ 사업관리(입양기록물관리) 5급
+ 아래의 자격요건을 모두 충족하는 자(①+②)
+ ① 다음의 어느 하나에 따라 기록물관리 전문요원 자격증을 소지한 자
+  - 기록관리학 전공으로 석사학위 이상을 취득한 자
+  - 기록관리학 학사학위 취득자, 역사학 또는 문헌정보학 학사학위 이상 취득자로서 행정안전부령으로 정하는 기록관리학 교육과정을 이수하고, 행정안전부장관이 시행하는 기록물관리 전문요원 시험에 합격한 자
+ ② 다음 각 자격요건 중 하나 이상에 해당하는 자
+  - 국가 또는 지방공무원 8급직 이상에 재직한 자
+  - 국가 또는 지방공무원 9급에 2년 이상 재직한 자
+  - 공공기관 또는 정부투자기관에서 5급 상당직으로 재직한 자
+  - 기록물관리 관련 업무 분야에서 2년 이상 근무한 자
+○ 사업관리(보훈) 6급
+「국가유공자 등 예우 및 지원에 관한 법률」 등 보훈관계법률에 따른 ‘취업지원대상자’에 해당하는 자로서, 아래 요건을 모두 충족하는 자
+ - 서울지방보훈청에서 보장원에 추천한 자
+ - 해당 직무를 수행할 수 있다고 인정되는 자(경력 및 학력 제한 없음)
+○ 사업관리(장애) 6급
+「장애인고용촉진 및 직업재활법」에 따른 ‘장애인’에 해당하는 자(경력 및 학력 제한 없음)
+○ 사업관리 6급, 기관운영(경영지원(비서)) 6급상당, 사업관리(입양인지원) 6급상당
+해당 직무를 수행할 수 있다고 인정되는 자(경력 및 학력 제한 없음)</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>취업지원대상자, 장애인, 자립준비청년, 비수도권지역인재, 고졸자, 청년인턴 수료자, 보장원 근무경력자, 한국사능력검정시험 인증서 소지자, 공인어학능력시험 성적 소지자 등 - 보다 자세한 사항은 첨부파일의 채용공고문을 참조</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>학력무관,대졸(4년)</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>정규직,비정규직</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>alio-304953</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>(재)우체국시설관리단</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>(재)우체국시설관리단 현장직원 2026년도 11차 통합 채용 공고(기술, 경비, 미화, 기타)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>서울,부산,대전,충북,전북,경남</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>무기계약직,비정규직</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>사업관리,경비.청소</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>신입+경력</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>취업지원대상자(국가보훈 등), 직무관련 자격증 ※기타 자세한 사항은 채용공고문 참조</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>https://poma.hrdms.kr</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>근무관서 및 채용분야별 응시자격은 채용공고문 참조(https://poma.hrdms.kr)</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>취업지원대상자(국가보훈 등), 직무관련 자격증 ※기타 자세한 사항은 채용공고문 참조</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>무기계약직,비정규직</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>alio-304952</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>무역안보관리원</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026년도 하반기 무역안보관리원 무기계약직 신입직원 채용 공고</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>무기계약직</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>사업관리,경영.회계.사무</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>신입</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>고졸</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>ㅇ 국가보훈 대상자: 만점의 5% 또는 10% 가산점 부여(모든 전형)
+ㅇ 장애인: 만점의 5% 가산점 부여(모든 전형)
+ㅇ 기초생활수급자, 한부모가정, 경력단절여성, 다문화가정, 북한이탈주민: 만점의 3%(서류 전형)
+ㅇ 자립준비청년: 만점의 5%(서류 전형)
+ㅇ 청년인턴: 최근 5년 이내 무역안보관리원 인턴으로 3개월 이상 근무한 자 만점의 3%</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>https://kosti.recruiter.co.kr/</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>ㅇ 연령(만 60세 미만인자), 성별, 경력 등 무관
+ㅇ 남자의 경우 병역 기피사실이 없는 자
+ㅇ 고졸인재</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>국가보훈 대상자, 장애인, 기초생활수급자, 한부모가정, 경력단절여성, 다문화가정, 북한이탈주민, 자립준비청년, 청년인턴, 비수도권지역인재, 한국사능력</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>고졸</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>무기계약직</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>alio-304951</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>무역안보관리원</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026년도 하반기 무역안보관리원 정규직 신입직원 채용 공고</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>사업관리,경영.회계.사무,전기.전자</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>신입</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>ㅇ 국가보훈 대상자: 만점의 5% 또는 10% 가산점 부여(모든 전형)
+ㅇ 장애인: 만점의 5% 가산점 부여(모든 전형)
+ㅇ 기초생활수급자, 한부모가정, 경력단절여성, 다문화가정, 북한이탈주민: 만점의 3%(서류 전형)
+ㅇ 자립준비청년: 만점의 5%(서류 전형)
+ㅇ 청년인턴: 최근 5년 이내 무역안보관리원 인턴으로 3개월 이상 근무한 자 만점의 3%</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>https://kosti.recruiter.co.kr/</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>ㅇ (전 부문 공통)
+- 학력, 연령(만 60세 미만인 자), 성별, 경력 등에 관계 없이 지원 가능
+- 남자의 경우 병역필 또는 면제자(병역 기피사실이 없는자)
+ㅇ 일반직 TOEIC 기준 800점 이상인 자
+ㅇ 연구직 TOEIC 기준 700점 이상인 자</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>국가보훈 대상자, 장애인, 기초생활수급자, 한부모가정, 경력단절여성, 다문화가정, 북한이탈주민, 자립준비청년, 청년인턴, 비수도권지역인재, 한국사능력</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>정규직</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>alio-304945</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한국연구재단</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026년 제2차 한국연구재단 직원 채용(연구직, 공무직(사무지원직))</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>서울,대전</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>정규직,무기계약직,청년인턴(채용형)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>사업관리,경영.회계.사무</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>신입</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>국가유공자, 장애인, 재단 체험형 인턴 우수인턴 지정자, 비수도권 지역 인재, 저소득층, 북한이탈주민, 다문화가족, 자립준비청년 우대
+※ 우대사항(가산점) 세부 기준은 공고문 참조 요망</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>https://www.nrf.re.kr/page/54?ac=view&amp;searchType=&amp;searchText=&amp;pageNum=1&amp;menuNo=54&amp;boardNo=7&amp;menuTypeCd=MENU_TYPE_02&amp;code=&amp;postNo=281928</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>공통: 해당 분야 직무기술서상의 직무역량을 보유하고, ’26. 12. 28.(월)부터 근무가 가능한 사람
+1. 나이 제한 없음. 단, 재단 정년을 고려하여 61세(입사일 기준) 미만인 사람(남성은 병역필 또는 면제자만 지원 가능. 병역법 제76조에 의한 병역의무 불이행 사실이 없는 자)
+2. 지원 자격요건을 참고하여 연구직 및 공무직 全 채용 분야 중 세부 1개 분야만 지원할 수 있으며, 이후 지원 분야 변경은 불가(이중(중복) 지원 적발 시, 지원 분야 모두 탈락)
+3. 세부 채용분야별 자격조건은 붙임자료 참조 요망</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>국가유공자, 장애인, 재단 체험형 인턴 우수인턴 지정자, 비수도권 지역 인재, 저소득층, 북한이탈주민, 다문화가족, 자립준비청년 우대</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>정규직,무기계약직,청년인턴(채용형)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>alio-304942</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>의료기관평가인증원</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>의료기관평가인증원 2026년 제3회 직원채용 공고</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>비정규직</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>사업관리,보건.의료</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>신입+경력</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>석사</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>1.「국가유공자 등 예우 및 지원에 관한 법률」 및 「보훈보상대상자 지원에 관한 법률」에 의한 ‘취업지원대상자’ * 이를 준용하는 법률에 의한 보훈 포함
+2.「장애인 고용촉진 및 직업재활법」에 따른 장애인 * 이를 준용하는 법률에 의한 장애인 포함
+3.「국민기초생활보장법」 제2조 제1호 및 제2호에 따른 수급(권)자 본인 또는 대상 가구의 구성원
+4.</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>https://koiha.recruiter.co.kr/career/home</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>○위촉연구원(연구원 다급)
+ - 관련분야 석사학위 소지자</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>취업지원대상자, 장애인, 저소득층, 비수도권 지역인재 등</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>석사</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>비정규직</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>alio-304936</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>근로복지공단</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>[서울서부지사] 공무직(시설방호원) 채용 공고</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>무기계약직</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>경비.청소</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>신입</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0 해당 법률에 의한 취업지원대상자
+- 「국가유공자 등 예우 및 지원에 관한 법률」 제29조에 따른 취업지원대상자(「독립유공자예우에 관한 법률」 제16조, 「보훈보상대상자 지원에 관한 법률」 제35조, 「고엽제후유의증 등 환자지원 및 단체설립에 관한 법률」 제7조의9, 「5·18 민주유공자예우 및 단체설립에 관한 법률」 제22조 또는 「특수임무유공자 예우</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>https://www.comwel.or.kr/recruit/hp/main.do</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>0 학력 및 경력 제한 없음
+0 국가공무원법 제33조 및 공단 인사규정 제14조 규정에 저촉되지 않는 자
+0 임용예정일 기준 공단 「공무직 및 기간제근로자의 인사복무 등 운영세칙」에 따른 정년 미도과자(60세 미만)
+0 병역법 제76조에서 정한 병역의무 불이행 사실이 없는 자
+- 현재 군복무 중인 경우 임용예정일 이전 전역이 가능한 자
+0 임용예정일 즉시 근무가 가능한 자
+- 임용일은 공단 사정에 따라 변경될 수 있음
+0 대한민국 국적을 보유한 자</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>취업지원대상자, 산재보험 장해 3급 이상 판정을 받은 자 본인, 산재사망 근로자 유자녀 또는 산재보험 장해 3급 이상 판정을 받은 자의 자녀, 장애인, 의상자 또는 의사자의 자녀, 기초생활수급자 및 차상위 계층자, 다문화가족, 북한이탈주민, 경력보유여성, 자립준비청년</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>무기계약직</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>alio-304922</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한국저작권위원회</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>한국저작권위원회 2026년 제3차 직원 채용</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>서울,경남</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>정규직,비정규직</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>사업관리,경영.회계.사무,문화.예술.디자인.방송</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>신입</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">○ 전단계 공통
+- 보훈취업지원대상자: 5점 ~ 10점
+- 장애인: 10점
+※ 가산대상이 2개 이상 중복되는 경우에는 가장 유리한 가점 1개만을 인정함
+※ 단, 분야별 채용예정 인원이 3명 이하인 경우「국가유공자 등 예우 및 지원에 관한 법률」제31조제3항에 따라 취업지원대상자 가점 적용을 아니하며, 같은 법 제31조제4항에 따라 선발예정인원을 </t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>https://copyright.recruiter.co.kr/</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>□ 자격
+- 공개경쟁 분야: 제한 없음
+- 제한경쟁 분야: 세부사항은 공고문 내 응시자격을 참고하시기 바랍니다.
+* 제한경쟁 분야: ③ 기간제계약직 학예일반
+□ 연령
+○ 정규직, 무기계약직, 기간제계약직
+- 제한 없음 (단, 2026.12.31. 기준 위원회 정년(만 60세)이 도래하는 자는 지원 불가)
+※ 상세내용 채용공고문 참고</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>보훈(취업지원대상자), 장애</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>정규직,비정규직</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>alio-304891</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한국무역보험공사</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>한국무역보험공사 2026년 하반기 지원직(무기계약직) 채용공고</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>서울</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>무기계약직</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>경영.회계.사무,운전.운송</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>신입</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>□ 별도 명시된 경우를 제외하고는, 입사지원서 접수 마감(‘26.9.29(화) 오전 11:00) 기준으로 유효하게 등록 또는 자격 취득(유지)자에 한함 
+□ 첨부파일 채용공고 ‘5. 증빙서류 제출’에 제시된 서류 제출이 가능한 경우에만 인정(입사지원시 서류발급 가능여부를 미리 확인)
+* 실제 대상자임에도 불구하고 입사지원시 우대사항을 기재(입력)하지 않</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>https://ksure-j.incruit.com</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>&lt;공통&gt;
+ㅇ 학력, 연령, 성별, 전공 제한 없는 열린 채용
+  - 단, 연령의 경우 만 60세 미만인 자
+ㅇ 남성의 경우 병역필(`26.11.22일(포함) 이전 전역예정자 포함) 또는 면제자
+ㅇ 공사 내규상 결격사유에 해당하지 않는 자 (첨부파일 [첨부4] 채용결격사유 참조)
+ㅇ 모든 채용전형, 연수에 참여가 가능하고 채용시(`26.12월 예정) 즉시 근무가 가능한 자
+&lt;사무지원(취업지원대상자)&gt;
+ㅇ 「국가유공자 등 예우 및 지원에 관한 법률」 등 보훈 관계법률에 의한 취업지원대상자
+ㅇ 한글, 엑셀, 파워포인트 등 OA활용이 가능한 자
+&lt;사무지원(장애인)&gt;
+ㅇ 「장애인고용촉진 및 직업재활법」에 의한 장애인
+ㅇ 한글, 엑셀, 파워포인트 등 OA활용이 가능한 자
+&lt;운전&gt;
+ㅇ 1종 보통 이상 운전면허 소지자로서, 임원 차량 운전 직무 2년 이상 경력 보유자
+ㅇ 최근 5년간 무사고 운전 경력 보유자
+ㅇ 최근 5년간 음주운전 경력이 없는 자</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">&lt;공통&gt; 취업지원대상자, 장애인, 비수도권 지역인재, 기초생활수급자, 차상위계층, 한부모가족지원대상자, 다문화가족 구성원, 자립지원 대상자, 북한이탈주민, &lt;사무지원(취업지원대상자, 장애인)&gt; 한국사능력검정시험(국사편찬위원회) 2급 이상 보유자, 직무 유관 자격증 보유자, &lt;운전&gt; 버스운전자격증 소지자 (보다 자세한 내용은 첨부파일 [첨부1] 한국무역보험공사 2026년 하반기 지원직(무기계약직) 채용공고 내 ‘4. 우대사항’ 참조) </t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>학력무관</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>엑셀</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>무기계약직</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>alio-304880</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>재단법인 한국장기조직기증원</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>(재)한국장기조직기증원 2026년 제4차 공개채용</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>서울,대전,전남광주</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>정규직,무기계약직,비정규직</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>경영.회계.사무,보건.의료</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>신입+경력</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>학력무관,대졸(2~3년),대졸(4년)</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>&lt; 공통 &gt;
+- 우대사항: 「장애인고용촉진 및 직업재활법 시행령」에 의한 장애인
+- 가점사항: 장기이식 수혜자, 뇌사 장기 기증자 및 사후 인체조직 기증자 유가족(4촌이내) 대상자, 장기·조직 기증희망 등록자, 국가유공자 등 예우 및 지원에 관한 법률 제29조에 의한 취업지원대상자
+- 장기조직코디네이터(정규5급)
+○ 400병상 이상 의료기관 근무</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>https://koda1458.recruiter.co.kr</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>- 판독전문의
+○ 진단검사의학과 전문의 자격 취득 후 이식면역검사 업무 2년 이상 경력자
+- 장기조직코디네이터(정규5급)
+○ 의료기관에서 2년 이상 환자 관리 업무를 수행한 간호사
+○ 타지역(전국) 발령 가능자
+- 간호사(정규6급)
+○ 간호사 면허증 소지자
+- 임상병리사(정규6급)
+○ 임상병리사 면허증 소지자
+○ 색각이상이 아닌 자
+- 행정(기획예산)(공무직)
+○ 경력 및 학력 등 제한 없음
+- 행정(회계)(공무직)
+○ 경력 및 학력 등 제한 없음
+- 간호사(계약직_육아휴직대체_서울,대전ㆍ광주)
+○ 간호사 면허증 소지자
+- 행정(회계)(계약직_육아휴직대체)
+○ 경력 및 학력 등 제한 없음
+- 행정(총무인사)(계약직_육아휴직대체)
+○ 경력 및 학력 등 제한 없음</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>○ 공통 : 장기이식 수혜자, 뇌사 장기 기증자 및 사후 인체조직 기증자 유가족(4촌이내) 대상자, 장기·조직 기증희망 등록자, 국가유공자 등 예우 및 지원에 관한 법률 제29조에 의한 취업지원대상자, 장애인고용촉진 및 직업재활법 시행령에 의한 장애인 *보다 자세한 사항은 첨부파일의 채용공고문을 참조</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>학력무관,대졸(2~3년),대졸(4년)</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>정규직,무기계약직,비정규직</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>alio-304773</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>잡알리오</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026년 4기 체험형 청년인턴 모집</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>서울,부산,대구,인천,대전,울산,경기,강원,충북,충남,전북,전남광주,경북,경남</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>청년인턴(체험형)</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>경영.회계.사무</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>신입</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>고졸</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>영어 SPEAKING(TOEIC Speaking, OPIc IM이상), 자격증, 지역아동센터 봉사(20시간 이상), 사회형평(자립준비청년,북한이탈주민), 자세한 내용은 공고문 내용 참고</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>https://kotra.applyin.co.kr/jobs/23263</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>가. 국적 : 대한민국 국적 소지자
+나. 응시연령 : 만 34세 이하 청년
+다. 학력 : 고등학교 졸업 이상('26. 9. 14. 공고일 기준)
+라. 최종 합격 후 근로계약 체결일(채용일)부터 근무 가능한 자</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>영어 SPEAKING(TOEIC Speaking, OPIc IM이상), 자격증, 지역아동센터 봉사(20시간 이상), 사회형평(자립준비청년,북한이탈주민), 자세한 내용은 공고문 내용 참고</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>고졸</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>청년인턴(체험형)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
